--- a/data/Sirok 2026 kontaktok.xlsx
+++ b/data/Sirok 2026 kontaktok.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paszt\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB7543CF-3A54-46EC-AF89-038EFC45EF91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9459D9-D4F1-4074-85B4-D8E23E8C2656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>Sirok 2026 – dolgozói kontaktlista</t>
   </si>
@@ -224,6 +224,9 @@
   </si>
   <si>
     <t>+36701730286</t>
+  </si>
+  <si>
+    <t>+36703429359</t>
   </si>
 </sst>
 </file>
@@ -723,7 +726,9 @@
       <c r="A22" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B22" s="3"/>
+      <c r="B22" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="C22" s="4"/>
     </row>
     <row r="23" spans="1:3" ht="24" customHeight="1">

--- a/data/Sirok 2026 kontaktok.xlsx
+++ b/data/Sirok 2026 kontaktok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paszt\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE9459D9-D4F1-4074-85B4-D8E23E8C2656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C9C62A-07CC-48F3-B5BD-1FF3284EBFF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
   <si>
     <t>Sirok 2026 – dolgozói kontaktlista</t>
   </si>
@@ -227,6 +227,12 @@
   </si>
   <si>
     <t>+36703429359</t>
+  </si>
+  <si>
+    <t>Fónad Dávid</t>
+  </si>
+  <si>
+    <t>+36302606907</t>
   </si>
 </sst>
 </file>
@@ -330,8 +336,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="contacts" displayName="contacts" ref="A4:C36" totalsRowShown="0">
-  <autoFilter ref="A4:C36" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="contacts" displayName="contacts" ref="A4:C37" totalsRowShown="0">
+  <autoFilter ref="A4:C37" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Név"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Telefonszám"/>
@@ -536,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -625,237 +631,246 @@
     </row>
     <row r="11" spans="1:3" ht="24" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="C11" s="4"/>
     </row>
     <row r="12" spans="1:3" ht="24" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C12" s="4"/>
     </row>
     <row r="13" spans="1:3" ht="24" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="4"/>
     </row>
     <row r="14" spans="1:3" ht="24" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C14" s="4"/>
     </row>
     <row r="15" spans="1:3" ht="24" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C15" s="4"/>
     </row>
     <row r="16" spans="1:3" ht="24" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C16" s="4"/>
     </row>
     <row r="17" spans="1:3" ht="24" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C17" s="4"/>
     </row>
     <row r="18" spans="1:3" ht="24" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C18" s="4"/>
     </row>
     <row r="19" spans="1:3" ht="24" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C19" s="4"/>
     </row>
     <row r="20" spans="1:3" ht="24" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C20" s="4"/>
     </row>
     <row r="21" spans="1:3" ht="24" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C21" s="4"/>
     </row>
     <row r="22" spans="1:3" ht="24" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="C22" s="4"/>
     </row>
     <row r="23" spans="1:3" ht="24" customHeight="1">
       <c r="A23" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="C23" s="4"/>
     </row>
     <row r="24" spans="1:3" ht="24" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C24" s="4"/>
     </row>
     <row r="25" spans="1:3" ht="24" customHeight="1">
       <c r="A25" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C25" s="4"/>
     </row>
     <row r="26" spans="1:3" ht="24" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C26" s="4"/>
     </row>
     <row r="27" spans="1:3" ht="24" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C27" s="4"/>
     </row>
     <row r="28" spans="1:3" ht="24" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C28" s="4"/>
     </row>
     <row r="29" spans="1:3" ht="24" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C29" s="4"/>
     </row>
     <row r="30" spans="1:3" ht="24" customHeight="1">
       <c r="A30" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C30" s="4"/>
     </row>
     <row r="31" spans="1:3" ht="24" customHeight="1">
       <c r="A31" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C31" s="4"/>
     </row>
     <row r="32" spans="1:3" ht="24" customHeight="1">
       <c r="A32" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C32" s="4"/>
     </row>
     <row r="33" spans="1:3" ht="24" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C33" s="4"/>
     </row>
     <row r="34" spans="1:3" ht="24" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C34" s="4"/>
     </row>
     <row r="35" spans="1:3" ht="24" customHeight="1">
       <c r="A35" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C35" s="4"/>
     </row>
     <row r="36" spans="1:3" ht="24" customHeight="1">
       <c r="A36" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C36" s="4"/>
+    </row>
+    <row r="37" spans="1:3" ht="24" customHeight="1">
+      <c r="A37" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B37" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C36" s="4"/>
+      <c r="C37" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/data/Sirok 2026 kontaktok.xlsx
+++ b/data/Sirok 2026 kontaktok.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paszt\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C9C62A-07CC-48F3-B5BD-1FF3284EBFF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C8D4221-77A3-4C1B-A65F-8D2A2AA67B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>Sirok 2026 – dolgozói kontaktlista</t>
   </si>
@@ -43,9 +43,6 @@
     <t>Csoma Gábor</t>
   </si>
   <si>
-    <t>Dobos Ádám</t>
-  </si>
-  <si>
     <t>Dorkó László</t>
   </si>
   <si>
@@ -137,9 +134,6 @@
   </si>
   <si>
     <t>+36309674363</t>
-  </si>
-  <si>
-    <t>+36209238377</t>
   </si>
   <si>
     <t>+36202300670</t>
@@ -336,8 +330,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="contacts" displayName="contacts" ref="A4:C37" totalsRowShown="0">
-  <autoFilter ref="A4:C37" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="contacts" displayName="contacts" ref="A4:C36" totalsRowShown="0">
+  <autoFilter ref="A4:C36" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Név"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Telefonszám"/>
@@ -542,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -580,7 +574,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C5" s="4"/>
     </row>
@@ -589,7 +583,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C6" s="4"/>
     </row>
@@ -598,7 +592,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C7" s="4"/>
     </row>
@@ -607,7 +601,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C8" s="4"/>
     </row>
@@ -616,25 +610,25 @@
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C9" s="4"/>
     </row>
     <row r="10" spans="1:3" ht="24" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>10</v>
+        <v>67</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="C10" s="4"/>
     </row>
     <row r="11" spans="1:3" ht="24" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="C11" s="4"/>
     </row>
@@ -643,7 +637,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C12" s="4"/>
     </row>
@@ -652,7 +646,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="4"/>
     </row>
@@ -661,7 +655,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" s="4"/>
     </row>
@@ -670,7 +664,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" s="4"/>
     </row>
@@ -679,7 +673,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" s="4"/>
     </row>
@@ -688,7 +682,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C17" s="4"/>
     </row>
@@ -697,7 +691,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C18" s="4"/>
     </row>
@@ -706,7 +700,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C19" s="4"/>
     </row>
@@ -715,7 +709,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C20" s="4"/>
     </row>
@@ -724,7 +718,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C21" s="4"/>
     </row>
@@ -733,7 +727,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="C22" s="4"/>
     </row>
@@ -742,7 +736,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="C23" s="4"/>
     </row>
@@ -751,7 +745,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C24" s="4"/>
     </row>
@@ -760,7 +754,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C25" s="4"/>
     </row>
@@ -769,7 +763,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C26" s="4"/>
     </row>
@@ -778,7 +772,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C27" s="4"/>
     </row>
@@ -787,7 +781,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C28" s="4"/>
     </row>
@@ -796,7 +790,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C29" s="4"/>
     </row>
@@ -805,7 +799,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C30" s="4"/>
     </row>
@@ -814,7 +808,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C31" s="4"/>
     </row>
@@ -823,7 +817,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C32" s="4"/>
     </row>
@@ -832,7 +826,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C33" s="4"/>
     </row>
@@ -841,7 +835,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C34" s="4"/>
     </row>
@@ -850,7 +844,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C35" s="4"/>
     </row>
@@ -859,18 +853,9 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C36" s="4"/>
-    </row>
-    <row r="37" spans="1:3" ht="24" customHeight="1">
-      <c r="A37" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C37" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/data/Sirok 2026 kontaktok.xlsx
+++ b/data/Sirok 2026 kontaktok.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paszt\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C8D4221-77A3-4C1B-A65F-8D2A2AA67B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE768866-0469-45CF-B7C1-274ABB2F1FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2010" yWindow="3195" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Kontaktok" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
   <si>
     <t>Sirok 2026 – dolgozói kontaktlista</t>
   </si>
@@ -118,9 +118,6 @@
     <t>Tóth István</t>
   </si>
   <si>
-    <t>Veres Valentin</t>
-  </si>
-  <si>
     <t>Vilmányi Zsolt</t>
   </si>
   <si>
@@ -203,9 +200,6 @@
   </si>
   <si>
     <t>+36707321007</t>
-  </si>
-  <si>
-    <t>+36303947056</t>
   </si>
   <si>
     <t>+36706282678</t>
@@ -330,8 +324,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="contacts" displayName="contacts" ref="A4:C36" totalsRowShown="0">
-  <autoFilter ref="A4:C36" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="contacts" displayName="contacts" ref="A4:C35" totalsRowShown="0">
+  <autoFilter ref="A4:C35" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Név"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Telefonszám"/>
@@ -536,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -574,7 +568,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" s="4"/>
     </row>
@@ -583,7 +577,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6" s="4"/>
     </row>
@@ -592,7 +586,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C7" s="4"/>
     </row>
@@ -601,7 +595,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8" s="4"/>
     </row>
@@ -610,16 +604,16 @@
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9" s="4"/>
     </row>
     <row r="10" spans="1:3" ht="24" customHeight="1">
       <c r="A10" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C10" s="4"/>
     </row>
@@ -628,7 +622,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11" s="4"/>
     </row>
@@ -637,7 +631,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" s="4"/>
     </row>
@@ -646,7 +640,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="4"/>
     </row>
@@ -655,7 +649,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C14" s="4"/>
     </row>
@@ -664,7 +658,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" s="4"/>
     </row>
@@ -673,7 +667,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C16" s="4"/>
     </row>
@@ -682,7 +676,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C17" s="4"/>
     </row>
@@ -691,7 +685,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18" s="4"/>
     </row>
@@ -700,7 +694,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C19" s="4"/>
     </row>
@@ -709,7 +703,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C20" s="4"/>
     </row>
@@ -718,7 +712,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C21" s="4"/>
     </row>
@@ -727,7 +721,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C22" s="4"/>
     </row>
@@ -736,7 +730,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C23" s="4"/>
     </row>
@@ -745,7 +739,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C24" s="4"/>
     </row>
@@ -754,7 +748,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C25" s="4"/>
     </row>
@@ -763,7 +757,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C26" s="4"/>
     </row>
@@ -772,7 +766,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C27" s="4"/>
     </row>
@@ -781,7 +775,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C28" s="4"/>
     </row>
@@ -790,7 +784,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C29" s="4"/>
     </row>
@@ -799,7 +793,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C30" s="4"/>
     </row>
@@ -808,7 +802,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C31" s="4"/>
     </row>
@@ -817,7 +811,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C32" s="4"/>
     </row>
@@ -826,7 +820,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C33" s="4"/>
     </row>
@@ -835,7 +829,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C34" s="4"/>
     </row>
@@ -844,18 +838,9 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C35" s="4"/>
-    </row>
-    <row r="36" spans="1:3" ht="24" customHeight="1">
-      <c r="A36" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C36" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/data/Sirok 2026 kontaktok.xlsx
+++ b/data/Sirok 2026 kontaktok.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paszt\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE768866-0469-45CF-B7C1-274ABB2F1FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ACAC74B-ACF0-4C9B-8841-CB1473C9528C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2010" yWindow="3195" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Kontaktok" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>Sirok 2026 – dolgozói kontaktlista</t>
   </si>
@@ -221,6 +221,12 @@
   </si>
   <si>
     <t>+36302606907</t>
+  </si>
+  <si>
+    <t>Veres Valentin</t>
+  </si>
+  <si>
+    <t>+36303947056</t>
   </si>
 </sst>
 </file>
@@ -324,8 +330,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="contacts" displayName="contacts" ref="A4:C35" totalsRowShown="0">
-  <autoFilter ref="A4:C35" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="contacts" displayName="contacts" ref="A4:C36" totalsRowShown="0">
+  <autoFilter ref="A4:C36" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Név"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Telefonszám"/>
@@ -530,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -817,30 +823,39 @@
     </row>
     <row r="33" spans="1:3" ht="24" customHeight="1">
       <c r="A33" s="2" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C33" s="4"/>
     </row>
     <row r="34" spans="1:3" ht="24" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C34" s="4"/>
     </row>
     <row r="35" spans="1:3" ht="24" customHeight="1">
       <c r="A35" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C35" s="4"/>
+    </row>
+    <row r="36" spans="1:3" ht="24" customHeight="1">
+      <c r="A36" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B36" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C35" s="4"/>
+      <c r="C36" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">
